--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BF9721-2923-425D-9C1E-01E3EE0CF388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFA31F9-F836-4B0E-99EF-8BD950DD83C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -305,14 +305,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>贴片电阻240欧姆0805封装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>R5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -336,10 +328,6 @@
   </si>
   <si>
     <t>10k-0805</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1k-0805</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -498,6 +486,18 @@
   </si>
   <si>
     <t>各类焊接工具：电烙铁、焊锡丝、镊子、热熔胶/胶枪等等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R6 /LCD-R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贴片电阻240欧姆0805封装/ 注LCD转接板背面的R1需要焊接此电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1k-0805 / 这里的R1指的是主板上的R1，转接板上的R1请焊接240R</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2938,7 +2938,7 @@
     <col min="3" max="3" width="13.88671875" customWidth="1"/>
     <col min="4" max="4" width="9.77734375" customWidth="1"/>
     <col min="5" max="5" width="44.44140625" customWidth="1"/>
-    <col min="6" max="6" width="59.88671875" customWidth="1"/>
+    <col min="6" max="6" width="65.109375" customWidth="1"/>
     <col min="7" max="7" width="12.88671875" customWidth="1"/>
     <col min="9" max="9" width="8.33203125" customWidth="1"/>
   </cols>
@@ -2954,7 +2954,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
@@ -2973,16 +2973,16 @@
     </row>
     <row r="3" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -3086,14 +3086,14 @@
     </row>
     <row r="13" spans="2:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -3186,13 +3186,13 @@
         <v>240</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3200,144 +3200,144 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
         <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
         <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
       </c>
       <c r="D23">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="32" spans="1:6" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="35" spans="2:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
         <v>44</v>
@@ -3442,7 +3442,7 @@
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -3481,12 +3481,12 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -3507,7 +3507,7 @@
     </row>
     <row r="47" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="53" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>
